--- a/annotators/team/tg/annotated/bbc.242418.xlsx
+++ b/annotators/team/tg/annotated/bbc.242418.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\in-progress\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\annotated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3C57EC-26A3-4984-A74A-3145C7F480F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A2CDFA-1E1A-41F4-9FCF-B0212CE6FF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="14292" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2124" windowWidth="16368" windowHeight="10836" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sentence-level annotation" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="486">
   <si>
     <t>ID</t>
   </si>
@@ -7810,9 +7810,7 @@
       <c r="F155" s="22" t="s">
         <v>453</v>
       </c>
-      <c r="G155" s="23" t="s">
-        <v>116</v>
-      </c>
+      <c r="G155" s="23"/>
       <c r="H155" s="24" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
@@ -8027,7 +8025,7 @@
         <v>OLD</v>
       </c>
       <c r="G161" s="23" t="s">
-        <v>430</v>
+        <v>479</v>
       </c>
       <c r="H161" s="24" t="str">
         <f t="shared" ca="1" si="17"/>

--- a/annotators/team/tg/annotated/bbc.242418.xlsx
+++ b/annotators/team/tg/annotated/bbc.242418.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\annotated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A2CDFA-1E1A-41F4-9FCF-B0212CE6FF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6C5A7D-6EE6-4AB9-84F8-E4862D9A53C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2124" windowWidth="16368" windowHeight="10836" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sentence-level annotation" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="487">
   <si>
     <t>ID</t>
   </si>
@@ -1472,13 +1472,16 @@
     <t>auch TYPE denkbar</t>
   </si>
   <si>
-    <t>johnson_mccoy</t>
-  </si>
-  <si>
     <t>siehe log</t>
   </si>
   <si>
     <t>event</t>
+  </si>
+  <si>
+    <t>anthony_mccoy</t>
+  </si>
+  <si>
+    <t>richard_johnson</t>
   </si>
 </sst>
 </file>
@@ -5151,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="26" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -8451,7 +8454,7 @@
         <v>126</v>
       </c>
       <c r="E175" s="21" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F175" s="22" t="s">
         <v>466</v>
@@ -8675,7 +8678,7 @@
         <v>126</v>
       </c>
       <c r="E181" s="21" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F181" s="22" t="s">
         <v>452</v>
@@ -8890,7 +8893,7 @@
         <v>126</v>
       </c>
       <c r="E187" s="21" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F187" s="22" t="s">
         <v>452</v>
@@ -10005,15 +10008,11 @@
       <c r="C224" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="E224" s="21" t="s">
-        <v>483</v>
-      </c>
+      <c r="E224" s="21"/>
       <c r="F224" s="22" t="s">
-        <v>466</v>
-      </c>
-      <c r="G224" s="23" t="s">
-        <v>479</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="G224" s="23"/>
       <c r="H224" s="24" t="str">
         <f t="shared" ca="1" si="25"/>
         <v/>
@@ -10356,21 +10355,22 @@
         <v/>
       </c>
       <c r="L233" s="26" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>276</v>
       </c>
-      <c r="E234" s="21"/>
+      <c r="E234" s="21" t="s">
+        <v>486</v>
+      </c>
       <c r="F234" s="22" t="str">
         <f>IF(OR(E234="",E234="!!!"),"",IF(NOT(ISNA(VLOOKUP(E234,E$1:E233,1,FALSE()))),"OLD",IF(AND(E234&lt;&gt;"",E234&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
-      </c>
-      <c r="G234" s="23" t="str">
-        <f>IF(OR(E234="",E234="!!!"),"",IF(OR(J234=0,AND(J234=1,K234=1),AND(J234=1,I234="SBJ"),AND(J234=1,I234=0)),"?IN_FOCUS",IF(J234&lt;=2,"?ACTIVATED",IF(J234&lt;&gt;"","?FAMILIAR",IF(F234="NEW",IF(ISNA(VLOOKUP(E234,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <v>NEW</v>
+      </c>
+      <c r="G234" s="23" t="s">
+        <v>479</v>
       </c>
       <c r="H234" s="24" t="str">
         <f t="shared" ca="1" si="25"/>
@@ -10574,9 +10574,7 @@
         <v>126</v>
       </c>
       <c r="E240" s="21"/>
-      <c r="F240" s="22" t="s">
-        <v>433</v>
-      </c>
+      <c r="F240" s="22"/>
       <c r="G240" s="23" t="str">
         <f>IF(OR(E240="",E240="!!!"),"",IF(OR(J240=0,AND(J240=1,K240=1),AND(J240=1,I240="SBJ"),AND(J240=1,I240=0)),"?IN_FOCUS",IF(J240&lt;=2,"?ACTIVATED",IF(J240&lt;&gt;"","?FAMILIAR",IF(F240="NEW",IF(ISNA(VLOOKUP(E240,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
         <v/>
@@ -10598,7 +10596,7 @@
         <v/>
       </c>
       <c r="L240" s="26" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.3">
@@ -10614,13 +10612,14 @@
       <c r="D241" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="E241" s="21"/>
+      <c r="E241" s="21" t="s">
+        <v>485</v>
+      </c>
       <c r="F241" s="22" t="s">
-        <v>433</v>
-      </c>
-      <c r="G241" s="23" t="str">
-        <f>IF(OR(E241="",E241="!!!"),"",IF(OR(J241=0,AND(J241=1,K241=1),AND(J241=1,I241="SBJ"),AND(J241=1,I241=0)),"?IN_FOCUS",IF(J241&lt;=2,"?ACTIVATED",IF(J241&lt;&gt;"","?FAMILIAR",IF(F241="NEW",IF(ISNA(VLOOKUP(E241,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <v>466</v>
+      </c>
+      <c r="G241" s="23" t="s">
+        <v>479</v>
       </c>
       <c r="H241" s="24" t="str">
         <f t="shared" ca="1" si="25"/>
